--- a/光伏配储项目/电价数据/2026/雨塘站.xlsx
+++ b/光伏配储项目/电价数据/2026/雨塘站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.55431</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.79781</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1.27749</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.21277</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.29446</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.34279</v>
+      </c>
+      <c r="H117" t="n">
+        <v>1.31649</v>
+      </c>
+      <c r="I117" t="n">
+        <v>1.31387</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44044</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.7896</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.8426900000000001</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.77519</v>
+      </c>
+      <c r="N117" t="n">
+        <v>1.32423</v>
+      </c>
+      <c r="O117" t="n">
+        <v>1.32406</v>
+      </c>
+      <c r="P117" t="n">
+        <v>1.32692</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.7684800000000001</v>
+      </c>
+      <c r="R117" t="n">
+        <v>1.31942</v>
+      </c>
+      <c r="S117" t="n">
+        <v>1.32208</v>
+      </c>
+      <c r="T117" t="n">
+        <v>1.3322</v>
+      </c>
+      <c r="U117" t="n">
+        <v>1.32524</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.83708</v>
+      </c>
+      <c r="W117" t="n">
+        <v>1.32132</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39495</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.7974600000000001</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>1.32185</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>1.3248</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.85307</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>1.349</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>1.42676</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.40517</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.89167</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.69814</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.69241</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.47327</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.76119</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.7844500000000001</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.40507</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.39563</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.05518</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>1.04499</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.13676</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.76174</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.72636</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.50968</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.41126</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.40743</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.41168</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.7942899999999999</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.9911799999999999</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.35369</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.53227</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.78855</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.43072</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.7968500000000001</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.7690399999999999</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.96651</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.9300700000000001</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.08123</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.35882</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.2197</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.26327</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.7509199999999999</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.261</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.20068</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.10756</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.25995</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.55242</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.31158</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.28881</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.50358</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.34566</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.26307</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.44418</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.38429</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.31669</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.81997</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47924</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.41067</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42191</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.19571</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.04739</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.18373</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53623</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5226499999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50627</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51674</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.86514</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.7676000000000001</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.83946</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.74619</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.73753</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.88512</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.81777</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.81525</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.8152200000000001</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.8180299999999999</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.79201</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.85853</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.19325</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.57055</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.09088</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.8435</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.73711</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.8064600000000001</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.70328</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.68913</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.9656699999999999</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.17824</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.80357</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.06351</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>1.02755</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.72994</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.5568099999999999</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.58013</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.7014199999999999</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.20645</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.27053</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.52123</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.20088</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.67523</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.09455</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.84954</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.28278</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.17437</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.29896</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.62679</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.65466</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.57689</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.62805</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.21753</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.20765</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.21515</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.20812</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>1.00629</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.18317</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.19831</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.19554</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.67686</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.20315</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20824</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.27164</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.56986</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.48726</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.2082</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.50606</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.26671</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.75807</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7637200000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.91395</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44059</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43462</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41392</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33341</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.79349</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1.02163</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.6855399999999999</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.79827</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.6898099999999999</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1.79669</v>
+      </c>
+      <c r="J119" t="n">
+        <v>1.04795</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1.03873</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.98372</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.82753</v>
+      </c>
+      <c r="N119" t="n">
+        <v>1.03763</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.81826</v>
+      </c>
+      <c r="P119" t="n">
+        <v>1.05124</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.69499</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.79818</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.6850700000000001</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.8035099999999999</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.81855</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.76359</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.81769</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.81412</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.71335</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.7099099999999999</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.8409800000000001</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.12186</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.88293</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.77028</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.71578</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.61019</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30781</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30099</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.64127</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.42662</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.18727</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.56673</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.69962</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.19682</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.6787</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.19694</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.20415</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.81133</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.97939</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.20638</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.20627</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.9105700000000001</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5638300000000001</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.41484</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.4775</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.68065</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.19204</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.05688</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.20463</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.44716</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.28931</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.20335</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.22452</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.21514</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.45491</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.29627</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.31103</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.67299</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.22258</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.21989</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.0752</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.10681</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.12767</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.11374</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.24426</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.1991</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.28748</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>1.02802</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.77224</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.72972</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.53983</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.41319</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34314</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.21425</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.9887</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.9709500000000001</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.9434600000000001</v>
+      </c>
+      <c r="H120" t="n">
+        <v>1.11223</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.79373</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.98438</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.8364299999999999</v>
+      </c>
+      <c r="N120" t="n">
+        <v>1.06453</v>
+      </c>
+      <c r="O120" t="n">
+        <v>1.04872</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.98302</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.81312</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.81528</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.57839</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.69892</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.58829</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.55562</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.8407100000000001</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.8119700000000001</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.98885</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.81851</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.7468899999999999</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.70228</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.56736</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.6888</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.72533</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.9434900000000001</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.20011</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.34373</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.8664400000000001</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.58606</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.67335</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.91444</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.8987200000000001</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.19344</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.44844</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.78012</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.9924500000000001</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.25417</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.7124199999999999</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.11766</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.53166</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.49372</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.6722400000000001</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>1.02999</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.13083</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.26835</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.20368</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.10576</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>1.0203</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.0365</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>1.00045</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.30243</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.48234</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.8172999999999999</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.38744</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.24001</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.86854</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>1.11116</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.19024</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.13602</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.19428</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.2904</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.3504</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.19408</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.30413</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.20627</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.19266</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.18611</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.22034</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.23379</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.2195</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.19649</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.19177</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.74551</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.53288</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.7498899999999999</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32204</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.7509</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.50052</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.40643</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.33697</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.48561</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.5121</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.53154</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.40663</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.43437</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.46379</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.73011</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.8637699999999999</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.62663</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.7150299999999999</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.74052</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.86133</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.71862</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.5614</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.56045</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.54901</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.6038</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.47992</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.10428</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.28848</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.55703</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.49325</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.52497</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.46946</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.65213</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.51373</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.49313</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.40369</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.4936</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.49675</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.61052</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.40689</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.51448</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.51325</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40956</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.4922</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.41134</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38194</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40555</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34435</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.22287</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1.00088</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1.0159</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.60058</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.8368</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.8711599999999999</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.78366</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.87098</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.88134</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.88164</v>
+      </c>
+      <c r="N122" t="n">
+        <v>1.32465</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.87666</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.8763200000000001</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.88203</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.8825299999999999</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.8823799999999999</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.27962</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.07514</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0428</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04374</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04177</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.04681</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.27543</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.08420999999999999</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.13152</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04446</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04653</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04642</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0.00368</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04495</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.30859</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04611</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04535</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.2708</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.28833</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.29638</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.39484</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.43125</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.44899</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.8535900000000001</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.87205</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.39497</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.39117</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.36533</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.39512</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.8649199999999999</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.87241</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.87239</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.36822</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.39806</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36514</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3346</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.76774</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.27985</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.30599</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.30445</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30841</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.28831</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15938</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27589</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.31236</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.30515</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.38951</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.76778</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.9052899999999999</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.69651</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.67059</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.68802</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.7709199999999999</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.97038</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.41589</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.48456</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.7487200000000001</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.75181</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.9167000000000001</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.71653</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.54964</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.48552</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.45787</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.09531999999999999</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29758</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.3782</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.38148</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.7470399999999999</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.75346</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.6569299999999999</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.61582</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.48069</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.7415499999999999</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79134</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.7921900000000001</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.6122000000000001</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.7561100000000001</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.03259</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.43482</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.8636699999999999</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.46467</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.35448</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.81543</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.40994</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.0679</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.4303</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.79116</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.46833</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.78895</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8011200000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303600000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78769</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78562</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87858</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87918</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50266</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41225</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46087</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21936</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6393799999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54143</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.8585499999999999</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.8618899999999999</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.86041</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.75934</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.8601</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.8664500000000001</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.72075</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.69374</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.73205</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38637</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.87266</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.88266</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.87619</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.87682</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.87897</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.86898</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.87878</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.8176599999999999</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.72272</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.8432799999999999</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.69377</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.60023</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43744</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.56496</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6671</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.07778</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.64871</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.50995</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.57799</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.59655</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.01065</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.34295</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.31167</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.27284</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.5614199999999999</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.80004</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.65722</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.5595</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.9938899999999999</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.7888500000000001</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.73749</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.65262</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.5846699999999999</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>1.02624</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>1.22053</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.5739</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.77871</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.7961699999999999</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.82952</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.7204299999999999</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.77266</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.95064</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.77806</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.7719</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.6136699999999999</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.59399</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.77343</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.82875</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.84524</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.83097</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.8215399999999999</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.7878999999999999</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.82578</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.81133</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.82256</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.83213</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.82889</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.82798</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.83129</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.84373</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.83197</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.8513999999999999</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.87222</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.86538</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.86812</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.8600399999999999</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.86764</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.87241</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.87578</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.7200800000000001</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95612</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.79823</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1.04817</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.9757400000000001</v>
+      </c>
+      <c r="H125" t="n">
+        <v>1.02735</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.8526900000000001</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.85139</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.75678</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.8131499999999999</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3754</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.36425</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.69372</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.66743</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.41165</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.5358200000000001</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.63173</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.7535299999999999</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.90439</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.15914</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.9429500000000001</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.56279</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.12752</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.8715000000000001</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.9802999999999999</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.88918</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.65618</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.10146</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.7935399999999999</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.53574</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.43893</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.37843</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.90815</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>1.27576</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>1.05417</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.24255</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.8111499999999999</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.8425499999999999</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>1.00573</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.7635</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.40898</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.39452</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.47845</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.36573</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.4451</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37127</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39766</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.50074</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.42059</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.41604</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59675</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.20117</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.51872</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70359</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79535</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64978</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5836399999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.80492</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.43968</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.77313</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.19419</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.93677</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.66004</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.71737</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.58169</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.17938</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.63858</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.92461</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.60301</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.6025</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.52576</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.49379</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.27535</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.54523</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.6184500000000001</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.87437</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.5322</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.7660800000000001</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.09961</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.09853</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.9768600000000001</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.99815</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.9520599999999999</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.18864</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.18937</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.89244</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.18923</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.63439</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>1.00128</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.04504</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.18933</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.9817899999999999</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>1.0228</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.6114</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.95409</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>1.01093</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1.11812</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.9154800000000001</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.90311</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.12825</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.62083</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.9899</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>1.02809</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.76061</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36891</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.34688</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.98019</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.82041</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.34677</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.75827</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.64266</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.7744500000000001</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>1.05902</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.82992</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.7691699999999999</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.82604</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.76406</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.81579</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.8361900000000001</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.7309099999999999</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>1.00208</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.8247000000000001</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>1.27211</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>1.62655</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.82677</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.82873</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.83048</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.7665</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.77049</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.83497</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.98699</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>1.01392</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.82674</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.70824</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.70153</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.71127</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.7135499999999999</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.37229</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.7055900000000001</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.4033</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.4054</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.7436</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.75218</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45677</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.7515499999999999</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.7573</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.75246</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.62426</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.5778799999999999</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46869</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.6362100000000001</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.9907100000000001</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.8753200000000001</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.8735700000000001</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.87701</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.89381</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.75785</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.80899</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.64436</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.52813</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.6447000000000001</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.52813</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.84549</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.88961</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.87526</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.8382500000000001</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.75944</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.7628400000000001</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.33358</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.5594600000000001</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.28232</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26678</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30668</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.47393</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31418</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.38422</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.48748</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.7062200000000001</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.60637</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.62639</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.8467100000000001</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.2673</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.16271</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.84994</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45035</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39625</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.42849</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.6999500000000001</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.93769</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.16445</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.11844</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.01513</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.54108</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.43854</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.42931</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39693</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49689</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44746</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.41404</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42611</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41871</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.56631</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.72548</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.7226</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.72549</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.66996</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.88297</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.54391</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.6704600000000001</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.54386</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.6679299999999999</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.74903</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.8801100000000001</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.77213</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.84546</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>1.28449</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.62768</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.41524</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.38898</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>1.00307</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.9917899999999999</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.99338</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.56058</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.55308</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.9434</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.08313</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.79309</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.01014</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.7771</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.65765</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.65038</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.71769</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.7963300000000001</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.29388</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.76546</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.35302</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.49009</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.16367</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.99114</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.65631</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.63308</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.66671</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.68008</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.67515</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.65213</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.67663</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.20672</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.70956</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.79134</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.70685</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.71462</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.72278</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.64156</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.75707</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.01855</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.12787</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.70069</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.70912</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.7029</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.78252</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.73268</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.82178</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.67275</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.46537</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.35378</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.73041</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.8457100000000001</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.7209</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.7544099999999999</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34499</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.71533</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.8659199999999999</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.45338</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.74117</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.88337</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.3926</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.75506</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.72765</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.93306</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.88432</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.88709</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.7577699999999999</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.35102</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.70653</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39824</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40272</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.42722</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.7549600000000001</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49549</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.51415</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.5226900000000001</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28473</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.40825</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.45368</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.93122</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.48463</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.19127</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.89985</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.7613099999999999</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.44955</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39416</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.45748</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.50003</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.50064</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.45104</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39307</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34929</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34372</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34298</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.40608</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.40611</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.7044400000000001</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.44175</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.40544</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.39407</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.45105</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.7545499999999999</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.42823</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.51861</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.70584</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.49904</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.40712</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.42043</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.42877</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.42307</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.56601</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38966</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.4267</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.4555</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.67028</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.45052</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.45205</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43036</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65181</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83157</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47207</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40267</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34479</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.78704</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.7521</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.74718</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1.5072</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.73548</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.63362</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.5810599999999999</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.48908</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.5249199999999999</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.48551</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.43875</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.51562</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.4182</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.54428</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.75951</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.76597</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.27883</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.4835</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.39378</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.54364</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.50076</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.71938</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.76014</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.55271</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.50085</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.45038</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.01747</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.4813</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.44208</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.09057</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.12637</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.07932</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.36937</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.11037</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.12704</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.01701</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.19274</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.14102</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.12991</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.17591</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.84192</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.19038</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.84797</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.33984</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.90086</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.70316</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.7555499999999999</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.94652</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.67203</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.80621</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.79516</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.9094800000000001</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.67887</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36016</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.76085</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.42036</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.4278</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.78118</v>
+      </c>
+      <c r="J133" t="n">
+        <v>1.09447</v>
+      </c>
+      <c r="K133" t="n">
+        <v>1.08097</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.79398</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.7762899999999999</v>
+      </c>
+      <c r="N133" t="n">
+        <v>1.00079</v>
+      </c>
+      <c r="O133" t="n">
+        <v>1.01656</v>
+      </c>
+      <c r="P133" t="n">
+        <v>1.02545</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.8084</v>
+      </c>
+      <c r="R133" t="n">
+        <v>1.05901</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.79898</v>
+      </c>
+      <c r="T133" t="n">
+        <v>1.02143</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.7134199999999999</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.63107</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.63328</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.63324</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.71689</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.50012</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.61411</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.47486</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.82101</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.65915</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.6142799999999999</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.96105</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.71153</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.12552</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.7653</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.30344</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.36374</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.74724</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.66898</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.37256</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>1.00675</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.61444</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.50215</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.50215</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.55043</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.6021799999999999</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.75476</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.20544</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.70857</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.9434199999999999</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.68362</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.9652200000000001</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.90906</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.7674</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.73716</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.18741</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.1886</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.45478</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.26893</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.67358</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.25643</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.29555</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.1192</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.44267</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.04302</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>1.11253</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>1.02982</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.45656</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.43054</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.72487</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.50952</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.61542</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.48756</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.44978</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.48861</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40533</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.5331900000000001</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39429</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.53532</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.79874</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.68698</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.66962</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.5029</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.08879</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.69613</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.6657</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.80362</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.08762</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.19926</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.50031</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.1998</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.5468500000000001</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.16015</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.5575599999999999</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.57063</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.42742</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.50271</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.23509</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.3737</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.42942</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.48311</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.4636</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.50802</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.51092</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.46032</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41266</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43362</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.5440900000000001</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.52224</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.6087</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38463</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4060299999999999</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38197</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39386</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36413</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.76197</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.14138</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.95666</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.8587400000000001</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.5354500000000001</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.46455</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.43936</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.41284</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.41213</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.39987</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.38119</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.42073</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.42126</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.43719</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.38418</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.50226</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.36786</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.46444</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.33314</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.30584</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.45056</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.41312</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.4467</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.59239</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.48512</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.45017</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.46421</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.45096</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.46528</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.55565</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.39296</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.45083</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.42577</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.4128</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37725</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.46171</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.42049</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.46957</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.7881699999999999</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.74139</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.74609</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.76458</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.72575</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.54027</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.47662</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.41361</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.41262</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1.13305</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.5413600000000001</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.79184</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.5404500000000001</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.53311</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.7073400000000001</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.69592</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.6956</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.35348</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.37281</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.38388</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.23484</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.27428</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.38983</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.16216</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.74494</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.22334</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.38962</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.27578</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.14907</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.48881</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.42231</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.70187</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.5699099999999999</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.29332</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.50152</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.38887</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.37618</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.39252</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.8859400000000001</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.36716</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.39332</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.36781</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.38348</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.40042</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.37246</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.40052</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.47793</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.46571</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.46826</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.40248</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.3935</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.38346</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.39362</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38299</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42943</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.81001</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39362</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38978</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.38971</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38649</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.40325</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.49195</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.10529</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.38974</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1.34645</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1.20694</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.52696</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.76262</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.7625700000000001</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.51622</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.41836</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.43013</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.42789</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.40998</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.41716</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.39654</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.38875</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.44622</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.5607000000000001</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.42819</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.38948</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.44567</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.77589</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>1.54044</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42665</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.8508</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.80572</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.45588</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.40411</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.7620399999999999</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.41324</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.53091</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.56147</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.56482</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.24939</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.09375</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.99326</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.32356</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.64146</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.5532999999999999</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.38991</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.49929</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.5854600000000001</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.7632899999999999</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.55196</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.5512400000000001</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.39718</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.24104</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.36378</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.76705</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.7641100000000001</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.5869099999999999</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.45379</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.4997799999999999</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>1.01909</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.77503</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.6303300000000001</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.7632599999999999</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.21113</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.61053</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.7559199999999999</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.6425700000000001</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.27442</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.90718</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.89128</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.9115800000000001</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.93015</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.18151</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.65355</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.96533</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.69786</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.9914299999999999</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.6672</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.68614</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.76492</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.66767</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.26865</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.04718</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.03182</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.04037</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.55562</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.36985</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.06096</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.41093</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.38173</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.76158</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.39017</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.3456</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.5604199999999999</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.80902</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.55349</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.7583200000000001</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.76015</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.56312</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.4713</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.46077</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40833</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.42983</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.42043</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.37111</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.38783</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.38399</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.36884</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.38373</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.40606</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.42802</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.64074</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.59711</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.56559</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.54418</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.45367</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.48347</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.5013500000000001</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.5612</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.8142</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.18241</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.13635</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.04924</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.13908</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.75484</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.74959</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.06008</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.07844</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.6870599999999999</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.5544199999999999</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.5608500000000001</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.5634</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.48061</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.28976</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.48841</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.55072</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.5503899999999999</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.5481</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.66318</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.55914</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.05427</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.6649400000000001</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.5508999999999999</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.5007</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.50088</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.48348</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.50071</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.48308</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.5008899999999999</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.57925</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.55876</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.56255</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.49895</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.5149</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.40376</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.40057</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.38474</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.42385</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.50137</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.5625800000000001</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.6629299999999999</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.18035</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.08393</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.66344</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.58469</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.16846</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.87301</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.66304</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.16834</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.84312</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.4982</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.51271</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.50008</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.4402</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.5360900000000001</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.39222</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34458</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1.21468</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.84709</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.85499</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1.40254</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.85998</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.5207000000000001</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.4357</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.4015</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.42042</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.43077</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.3937</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.36333</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35323</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.35421</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36167</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38753</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.6309900000000001</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.59129</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.43217</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.6451699999999999</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.0369</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.22475</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.93613</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.9919199999999999</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.03916</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.98277</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.95035</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.98109</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.96375</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.94865</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.95116</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.51344</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.94455</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1.32199</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.7998099999999999</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1.3178</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>1.39999</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.38184</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.7341599999999999</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.95382</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.87379</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.94076</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.55108</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.69611</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.71843</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.76679</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.21416</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.09437</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.03415</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.42209</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.34584</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.02963</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.12849</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.93357</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.7670399999999999</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.7662100000000001</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.82539</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.70921</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42434</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.69043</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.5545599999999999</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.69335</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.74382</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.70263</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.3687</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.76295</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40113</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40117</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40389</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36711</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.7128300000000001</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.46638</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.75252</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.52503</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.51164</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.44441</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.02954</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.92733</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.03916</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.93838</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.04698</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>1.02982</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.31522</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.4481</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.10006</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.37387</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.7337100000000001</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.39683</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.68357</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.62909</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.74017</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.72494</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.02264</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.72633</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.77935</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.1516</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.49926</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.71529</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.48222</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.64736</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>1.23441</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.68437</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.6636</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.70551</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.70732</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.81387</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.77073</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.8094600000000001</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.89064</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37511</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.5212599999999999</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38857</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.76127</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.43982</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.4506</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.38332</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.38101</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.50034</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38191</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.80883</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.30928</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.0011</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.93121</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.9574400000000001</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.03676</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.16442</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.07205</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.86146</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.69211</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.24099</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.2147</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.21607</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.14696</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.86363</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.7005</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.09189</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.10373</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.10384</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.13284</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.10146</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.51915</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.1969</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.66069</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.58599</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.15293</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.75161</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.68236</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.18123</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.87549</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.00571</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1.00765</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.01693</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.03913</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.06611</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.12453</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.04758</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.05819</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.18232</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.16137</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.05846</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.20115</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.30362</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.16726</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.0768</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.11699</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.09761</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.1239</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.17352</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.19085</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.17128</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>1.11826</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.6926599999999999</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.6289199999999999</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.57709</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.55744</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.44855</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.3791600000000001</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37558</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.54836</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.3097</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.30722</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.06489</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.48167</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.51919</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.58731</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39871</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.51764</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.5191399999999999</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.5615800000000001</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.5879800000000001</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.5601699999999999</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39333</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38503</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.57469</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.55862</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.56051</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.5640499999999999</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.56114</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.54961</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.53084</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.53251</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.5315</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.52401</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37244</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.8479500000000001</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.53298</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.37436</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.5785800000000001</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.70333</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.71892</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.67018</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.95884</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.77059</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.96424</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.17616</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.33073</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.47569</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.46261</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.45586</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.57369</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.8504299999999999</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.23912</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.7371799999999999</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.7000700000000001</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.50145</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.8437899999999999</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.88537</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.24999</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.77598</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.5791799999999999</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.58587</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.64646</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.72964</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.6086</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.7543200000000001</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.62939</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.21834</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.19234</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.41897</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.19446</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>1.19738</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>1.13058</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.10477</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.20688</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.13162</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.21774</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.07889</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>1.10807</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.20586</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.11409</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.55455</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.8108200000000001</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.8037300000000001</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.5638500000000001</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.38086</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.2344</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.84872</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.84922</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.55888</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.55438</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.5630299999999999</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.51532</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.5537300000000001</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.5210199999999999</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.5010899999999999</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.45961</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.45985</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38093</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36087</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43854</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.39901</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41202</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.49487</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.49896</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.54731</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.51973</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.52006</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.5569700000000001</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.17482</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.8824</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.49267</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.20648</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.50794</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.5700299999999999</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.84472</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.79571</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.59721</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.85181</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.50512</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.52101</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.54587</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.17593</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.70041</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.5544199999999999</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.18328</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.54836</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.54896</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.5802</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.79898</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.5539299999999999</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.79686</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.8484400000000001</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.17331</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.79798</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.68306</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1.09045</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.17494</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.18036</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.18458</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.18237</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.8218300000000001</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.7357400000000001</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.65562</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.68629</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.6949299999999999</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.73377</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.83287</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.81629</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.6224500000000001</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.81653</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.76549</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.14503</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.7688200000000001</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.60885</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.65264</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.64732</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.62082</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.61641</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.72209</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.67972</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.83008</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.70377</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.60795</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.53087</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.51236</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38405</v>
       </c>
     </row>
   </sheetData>
